--- a/data/trans_dic/P21B_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P21B_R2-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,09%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,45; 14,59</t>
+          <t>2,4; 15,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,05</t>
+          <t>0,0; 11,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,33; 20,7</t>
+          <t>4,58; 20,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,01; 26,82</t>
+          <t>12,62; 26,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 13,63</t>
+          <t>1,77; 14,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,63; 26,79</t>
+          <t>9,15; 26,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,85; 34,75</t>
+          <t>15,06; 36,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,31; 22,92</t>
+          <t>10,06; 21,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,02; 11,34</t>
+          <t>3,15; 11,31</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,62; 17,98</t>
+          <t>6,06; 17,55</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,63; 25,43</t>
+          <t>12,22; 25,1</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,34; 23,35</t>
+          <t>12,76; 21,93</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,64%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,28; 22,01</t>
+          <t>4,23; 23,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,51; 22,16</t>
+          <t>5,4; 21,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,03; 33,12</t>
+          <t>9,66; 33,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,69; 22,11</t>
+          <t>7,0; 22,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,3; 15,02</t>
+          <t>2,53; 15,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,02; 8,7</t>
+          <t>0,0; 8,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,03; 25,03</t>
+          <t>7,49; 23,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,64; 22,13</t>
+          <t>10,63; 22,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,72; 15,15</t>
+          <t>4,6; 15,59</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,15; 11,9</t>
+          <t>3,72; 13,09</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,18; 24,24</t>
+          <t>10,36; 23,52</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,67; 20,23</t>
+          <t>10,26; 20,05</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,94</t>
+          <t>0,0; 6,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,77</t>
+          <t>0,0; 3,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 13,08</t>
+          <t>1,25; 11,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,74; 14,67</t>
+          <t>2,71; 13,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,53</t>
+          <t>0,0; 12,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,97</t>
+          <t>0,0; 13,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,02; 26,76</t>
+          <t>3,11; 26,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,26; 11,5</t>
+          <t>2,23; 12,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,7; 6,26</t>
+          <t>0,69; 6,33</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,68</t>
+          <t>0,44; 3,82</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,47; 12,19</t>
+          <t>2,52; 12,27</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,32; 11,9</t>
+          <t>3,19; 11,34</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 5,03</t>
+          <t>0,85; 4,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1147,52 +1147,52 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,07; 7,1</t>
+          <t>1,09; 7,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 6,48</t>
+          <t>0,98; 6,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 5,11</t>
+          <t>0,52; 5,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 6,68</t>
+          <t>0,82; 6,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,78; 9,62</t>
+          <t>2,79; 10,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,54; 6,1</t>
+          <t>2,63; 8,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,79</t>
+          <t>0,97; 3,73</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,72</t>
+          <t>0,61; 3,61</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,7; 7,4</t>
+          <t>2,62; 7,09</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 4,56</t>
+          <t>2,07; 5,82</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,15</t>
+          <t>0,0; 19,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,93</t>
+          <t>0,0; 6,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,96; 8,56</t>
+          <t>1,01; 8,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,25; 21,05</t>
+          <t>1,83; 20,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,03</t>
+          <t>0,0; 4,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,49</t>
+          <t>0,42; 3,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,62; 5,23</t>
+          <t>0,62; 5,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,67; 6,23</t>
+          <t>1,9; 6,76</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,54; 7,14</t>
+          <t>0,77; 6,0</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,16</t>
+          <t>0,58; 3,27</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,15; 5,16</t>
+          <t>1,17; 5,03</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,19; 8,65</t>
+          <t>2,74; 9,23</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -1417,17 +1417,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,9</t>
+          <t>0,0; 11,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,66</t>
+          <t>0,0; 8,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,32; 18,56</t>
+          <t>3,46; 19,53</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1437,42 +1437,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,29</t>
+          <t>0,81; 4,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,33</t>
+          <t>0,35; 3,01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,77; 6,57</t>
+          <t>0,86; 6,7</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,7; 11,55</t>
+          <t>3,79; 12,47</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,17</t>
+          <t>0,9; 4,21</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,0</t>
+          <t>0,54; 3,03</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,07; 7,33</t>
+          <t>2,16; 7,93</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,63; 9,31</t>
+          <t>2,91; 10,12</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,73; 6,27</t>
+          <t>2,59; 6,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,58</t>
+          <t>1,4; 3,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,81; 9,34</t>
+          <t>4,74; 8,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,81; 10,43</t>
+          <t>5,85; 10,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,31</t>
+          <t>1,93; 4,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,99; 4,35</t>
+          <t>2,12; 4,54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,27; 9,42</t>
+          <t>5,27; 9,6</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,32; 8,53</t>
+          <t>6,25; 9,5</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,43; 4,5</t>
+          <t>2,49; 4,5</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,98; 3,67</t>
+          <t>1,99; 3,7</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5,47; 8,39</t>
+          <t>5,46; 8,44</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,59; 8,47</t>
+          <t>6,57; 9,15</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23381</t>
+          <t>24752</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17252</t>
+          <t>17764</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>40633</t>
+          <t>42516</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1913; 11407</t>
+          <t>1875; 12068</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6924</t>
+          <t>0; 6030</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2784; 13298</t>
+          <t>2942; 12940</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15801; 32570</t>
+          <t>16503; 34549</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>939; 9345</t>
+          <t>1211; 10104</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6903; 21426</t>
+          <t>7316; 21121</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11149; 26090</t>
+          <t>11303; 27609</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11242; 25000</t>
+          <t>11869; 25760</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4429; 16636</t>
+          <t>4616; 16586</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8810; 23913</t>
+          <t>8063; 23348</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16209; 35435</t>
+          <t>17031; 34966</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>30740; 53832</t>
+          <t>31740; 54551</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10050</t>
+          <t>10679</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>15410</t>
+          <t>17340</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>25460</t>
+          <t>28019</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2779; 14297</t>
+          <t>2750; 15156</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3211; 15780</t>
+          <t>3849; 15442</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5225; 17252</t>
+          <t>5033; 17367</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5184; 17146</t>
+          <t>5759; 18237</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2100; 13706</t>
+          <t>2306; 13827</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>886; 7541</t>
+          <t>0; 7129</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6527; 20343</t>
+          <t>6087; 18844</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10513; 21866</t>
+          <t>11607; 24123</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7364; 23660</t>
+          <t>7177; 24341</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4979; 18787</t>
+          <t>5875; 20668</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13573; 32320</t>
+          <t>13816; 31368</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18806; 35666</t>
+          <t>19629; 38364</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6418</t>
+          <t>6483</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3108</t>
+          <t>3403</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9526</t>
+          <t>9885</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 7658</t>
+          <t>0; 6207</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4321</t>
+          <t>0; 5560</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1100; 11559</t>
+          <t>1102; 9933</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2401; 12840</t>
+          <t>2623; 13311</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5856</t>
+          <t>0; 5823</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 7994</t>
+          <t>0; 7009</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>941; 8334</t>
+          <t>968; 8347</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1183; 6010</t>
+          <t>1311; 7379</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1000; 8957</t>
+          <t>987; 9065</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933; 7717</t>
+          <t>929; 8013</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2946; 14563</t>
+          <t>3016; 14656</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4635; 16639</t>
+          <t>4963; 17636</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6137</t>
+          <t>6465</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>10811</t>
+          <t>11746</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>16949</t>
+          <t>18211</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1863; 11314</t>
+          <t>1919; 11098</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2561,52 +2561,52 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1997; 13241</t>
+          <t>2039; 14257</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1947; 14640</t>
+          <t>2459; 15593</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>951; 9628</t>
+          <t>988; 9536</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1864; 14824</t>
+          <t>1809; 14903</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5507; 19039</t>
+          <t>5517; 19899</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2269; 25765</t>
+          <t>6463; 21126</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3897; 15681</t>
+          <t>4022; 15435</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2979; 17747</t>
+          <t>2893; 17214</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10388; 28422</t>
+          <t>10062; 27256</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4820; 29567</t>
+          <t>10262; 28795</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5651</t>
+          <t>7326</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6215</t>
+          <t>7576</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11866</t>
+          <t>14902</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 8909</t>
+          <t>0; 9424</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 5373</t>
+          <t>0; 6920</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>946; 8397</t>
+          <t>987; 8201</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1204; 20327</t>
+          <t>1996; 22107</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 5544</t>
+          <t>0; 5812</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>974; 8082</t>
+          <t>981; 8115</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>919; 7777</t>
+          <t>926; 7768</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2962; 11040</t>
+          <t>3784; 13474</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1016; 13314</t>
+          <t>1446; 11194</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1983; 10754</t>
+          <t>1972; 11146</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2843; 12734</t>
+          <t>2884; 12409</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5991; 23684</t>
+          <t>8455; 28498</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>10598</t>
+          <t>12496</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>10598</t>
+          <t>12497</t>
         </is>
       </c>
     </row>
@@ -2967,17 +2967,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4439</t>
+          <t>0; 5315</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5674</t>
+          <t>0; 4902</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2068; 11562</t>
+          <t>2157; 12164</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2987,42 +2987,42 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2137; 12502</t>
+          <t>2373; 12716</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>997; 10037</t>
+          <t>1059; 9091</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1661; 14138</t>
+          <t>1857; 14424</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5945; 18577</t>
+          <t>6642; 21852</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3112; 14021</t>
+          <t>3025; 14166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1920; 10807</t>
+          <t>1931; 10905</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5743; 20346</t>
+          <t>5986; 22014</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5444; 19269</t>
+          <t>6330; 22015</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>51638</t>
+          <t>55706</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>63394</t>
+          <t>70325</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>115032</t>
+          <t>126031</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>15263; 35006</t>
+          <t>14448; 35954</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>9004; 25171</t>
+          <t>9828; 26902</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>26552; 51514</t>
+          <t>26160; 49407</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>38048; 68350</t>
+          <t>41594; 72969</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>15672; 35543</t>
+          <t>15880; 35103</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19443; 42396</t>
+          <t>20630; 44295</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>39491; 70597</t>
+          <t>39470; 71959</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>33895; 87086</t>
+          <t>56572; 86081</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>33647; 62143</t>
+          <t>34462; 62244</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>33222; 61640</t>
+          <t>33309; 62123</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>71145; 109142</t>
+          <t>70960; 109790</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>76837; 141936</t>
+          <t>106310; 148001</t>
         </is>
       </c>
     </row>
